--- a/output/pdf_financials_xlsx/PALS.xlsx
+++ b/output/pdf_financials_xlsx/PALS.xlsx
@@ -1408,7 +1408,7 @@
         </is>
       </c>
       <c r="B92" s="3" t="n">
-        <v>0</v>
+        <v>0.27933</v>
       </c>
     </row>
     <row r="93">
@@ -2506,7 +2506,11 @@
           <t>Warrants reserve 525,540</t>
         </is>
       </c>
-      <c r="D27" t="inlineStr"/>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E27" s="5" t="n">
         <v>0.27933</v>
       </c>

--- a/output/pdf_financials_xlsx/PALS.xlsx
+++ b/output/pdf_financials_xlsx/PALS.xlsx
@@ -824,7 +824,7 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>0.596123</v>
       </c>
     </row>
     <row r="35">
@@ -844,7 +844,7 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>0.596123</v>
       </c>
     </row>
     <row r="37">
@@ -964,7 +964,7 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>0.669695</v>
+        <v>0.073572</v>
       </c>
     </row>
     <row r="49">
@@ -1928,7 +1928,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E3" s="5" t="n">

--- a/output/pdf_financials_xlsx/PALS.xlsx
+++ b/output/pdf_financials_xlsx/PALS.xlsx
@@ -1587,7 +1587,7 @@
         </is>
       </c>
       <c r="B110" s="3" t="n">
-        <v>0</v>
+        <v>1.026512</v>
       </c>
     </row>
     <row r="111">
@@ -3244,7 +3244,11 @@
           <t>Accretion expense 6 861,698</t>
         </is>
       </c>
-      <c r="D61" t="inlineStr"/>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>OtherNonCashItems</t>
+        </is>
+      </c>
       <c r="E61" s="5" t="n">
         <v>1.026512</v>
       </c>
